--- a/data/macro/USA/USPMI.xlsx
+++ b/data/macro/USA/USPMI.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9A504A-B720-3140-BEF9-01DE03EA2F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A509A3CC-D8E8-0443-8D53-CB09CCF01293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
+    <workbookView xWindow="16600" yWindow="780" windowWidth="19400" windowHeight="20700" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
   </bookViews>
   <sheets>
     <sheet name="NAPMPMI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,8 +66,8 @@
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -118,18 +118,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -467,13 +467,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF67A92-ADBD-0745-9FE5-B9C5971015D9}">
-  <dimension ref="A1:G671"/>
+  <dimension ref="A1:G674"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="3" customWidth="1"/>
     <col min="5" max="7" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -3109,7 +3109,7 @@
         <v>29252</v>
       </c>
       <c r="B124" s="1">
-        <v>29281</v>
+        <v>29283</v>
       </c>
       <c r="C124" s="2">
         <v>0.41666666666666669</v>
@@ -3172,7 +3172,7 @@
         <v>29342</v>
       </c>
       <c r="B127" s="1">
-        <v>29373</v>
+        <v>29374</v>
       </c>
       <c r="C127" s="2">
         <v>0.41666666666666669</v>
@@ -3235,7 +3235,7 @@
         <v>29434</v>
       </c>
       <c r="B130" s="1">
-        <v>29465</v>
+        <v>29466</v>
       </c>
       <c r="C130" s="2">
         <v>0.41666666666666669</v>
@@ -3292,7 +3292,7 @@
         <v>29495</v>
       </c>
       <c r="B132" s="1">
-        <v>29526</v>
+        <v>29528</v>
       </c>
       <c r="C132" s="2">
         <v>0.41666666666666669</v>
@@ -3334,7 +3334,7 @@
         <v>29556</v>
       </c>
       <c r="B134" s="1">
-        <v>29587</v>
+        <v>29588</v>
       </c>
       <c r="C134" s="2">
         <v>0.41666666666666669</v>
@@ -3355,7 +3355,7 @@
         <v>29587</v>
       </c>
       <c r="B135" s="1">
-        <v>29618</v>
+        <v>29619</v>
       </c>
       <c r="C135" s="2">
         <v>0.41666666666666669</v>
@@ -3376,7 +3376,7 @@
         <v>29618</v>
       </c>
       <c r="B136" s="1">
-        <v>29646</v>
+        <v>29647</v>
       </c>
       <c r="C136" s="2">
         <v>0.41666666666666669</v>
@@ -3481,7 +3481,7 @@
         <v>29768</v>
       </c>
       <c r="B141" s="1">
-        <v>29799</v>
+        <v>29801</v>
       </c>
       <c r="C141" s="2">
         <v>0.41666666666666669</v>
@@ -3544,7 +3544,7 @@
         <v>29860</v>
       </c>
       <c r="B144" s="1">
-        <v>29891</v>
+        <v>29892</v>
       </c>
       <c r="C144" s="2">
         <v>0.41666666666666669</v>
@@ -3586,7 +3586,7 @@
         <v>29921</v>
       </c>
       <c r="B146" s="1">
-        <v>29952</v>
+        <v>29590</v>
       </c>
       <c r="C146" s="2">
         <v>0.41666666666666669</v>
@@ -3670,7 +3670,7 @@
         <v>30042</v>
       </c>
       <c r="B150" s="1">
-        <v>30072</v>
+        <v>30074</v>
       </c>
       <c r="C150" s="2">
         <v>0.41666666666666669</v>
@@ -3733,7 +3733,7 @@
         <v>30133</v>
       </c>
       <c r="B153" s="1">
-        <v>30164</v>
+        <v>30165</v>
       </c>
       <c r="C153" s="2">
         <v>0.41666666666666669</v>
@@ -3838,7 +3838,7 @@
         <v>30286</v>
       </c>
       <c r="B158" s="1">
-        <v>30317</v>
+        <v>30319</v>
       </c>
       <c r="C158" s="2">
         <v>0.41666666666666669</v>
@@ -3922,7 +3922,7 @@
         <v>30407</v>
       </c>
       <c r="B162" s="1">
-        <v>30437</v>
+        <v>30438</v>
       </c>
       <c r="C162" s="2">
         <v>0.41666666666666669</v>
@@ -4027,7 +4027,7 @@
         <v>30560</v>
       </c>
       <c r="B167" s="1">
-        <v>30590</v>
+        <v>30592</v>
       </c>
       <c r="C167" s="2">
         <v>0.41666666666666669</v>
@@ -4090,7 +4090,7 @@
         <v>30651</v>
       </c>
       <c r="B170" s="1">
-        <v>30682</v>
+        <v>30684</v>
       </c>
       <c r="C170" s="2">
         <v>0.41666666666666669</v>
@@ -4153,14 +4153,14 @@
         <v>30742</v>
       </c>
       <c r="B173" s="1">
-        <v>30773</v>
+        <v>30774</v>
       </c>
       <c r="C173" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D173" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E173" s="4">
         <v>58.9</v>
@@ -4216,7 +4216,7 @@
         <v>30834</v>
       </c>
       <c r="B176" s="1">
-        <v>30864</v>
+        <v>30865</v>
       </c>
       <c r="C176" s="2">
         <v>0.41666666666666669</v>
@@ -4258,7 +4258,7 @@
         <v>30895</v>
       </c>
       <c r="B178" s="1">
-        <v>30926</v>
+        <v>30929</v>
       </c>
       <c r="C178" s="2">
         <v>0.41666666666666669</v>
@@ -4321,7 +4321,7 @@
         <v>30987</v>
       </c>
       <c r="B181" s="1">
-        <v>31017</v>
+        <v>31019</v>
       </c>
       <c r="C181" s="2">
         <v>0.41666666666666669</v>
@@ -4342,7 +4342,7 @@
         <v>31017</v>
       </c>
       <c r="B182" s="1">
-        <v>31048</v>
+        <v>31049</v>
       </c>
       <c r="C182" s="2">
         <v>0.41666666666666669</v>
@@ -4447,7 +4447,7 @@
         <v>31168</v>
       </c>
       <c r="B187" s="1">
-        <v>31199</v>
+        <v>31201</v>
       </c>
       <c r="C187" s="2">
         <v>0.41666666666666669</v>
@@ -4510,7 +4510,7 @@
         <v>31260</v>
       </c>
       <c r="B190" s="1">
-        <v>31291</v>
+        <v>31293</v>
       </c>
       <c r="C190" s="2">
         <v>0.41666666666666669</v>
@@ -4573,7 +4573,7 @@
         <v>31352</v>
       </c>
       <c r="B193" s="1">
-        <v>31382</v>
+        <v>31383</v>
       </c>
       <c r="C193" s="2">
         <v>0.41666666666666669</v>
@@ -4594,7 +4594,7 @@
         <v>31382</v>
       </c>
       <c r="B194" s="1">
-        <v>31413</v>
+        <v>31414</v>
       </c>
       <c r="C194" s="2">
         <v>0.41666666666666669</v>
@@ -4615,7 +4615,7 @@
         <v>31413</v>
       </c>
       <c r="B195" s="1">
-        <v>31444</v>
+        <v>31446</v>
       </c>
       <c r="C195" s="2">
         <v>0.41666666666666669</v>
@@ -4651,7 +4651,7 @@
         <v>31444</v>
       </c>
       <c r="B196" s="1">
-        <v>31472</v>
+        <v>31474</v>
       </c>
       <c r="C196" s="2">
         <v>0.41666666666666669</v>
@@ -4714,7 +4714,7 @@
         <v>31533</v>
       </c>
       <c r="B199" s="1">
-        <v>31564</v>
+        <v>31565</v>
       </c>
       <c r="C199" s="2">
         <v>0.41666666666666669</v>
@@ -4777,7 +4777,7 @@
         <v>31625</v>
       </c>
       <c r="B202" s="1">
-        <v>31656</v>
+        <v>31657</v>
       </c>
       <c r="C202" s="2">
         <v>0.41666666666666669</v>
@@ -4819,7 +4819,7 @@
         <v>31686</v>
       </c>
       <c r="B204" s="1">
-        <v>31717</v>
+        <v>31719</v>
       </c>
       <c r="C204" s="2">
         <v>0.41666666666666669</v>
@@ -4861,7 +4861,7 @@
         <v>31747</v>
       </c>
       <c r="B206" s="1">
-        <v>31778</v>
+        <v>31779</v>
       </c>
       <c r="C206" s="2">
         <v>0.41666666666666669</v>
@@ -4882,7 +4882,7 @@
         <v>31778</v>
       </c>
       <c r="B207" s="1">
-        <v>31809</v>
+        <v>31810</v>
       </c>
       <c r="C207" s="2">
         <v>0.41666666666666669</v>
@@ -4903,7 +4903,7 @@
         <v>31809</v>
       </c>
       <c r="B208" s="1">
-        <v>31837</v>
+        <v>31838</v>
       </c>
       <c r="C208" s="2">
         <v>0.41666666666666669</v>
@@ -5008,7 +5008,7 @@
         <v>31959</v>
       </c>
       <c r="B213" s="1">
-        <v>31990</v>
+        <v>31992</v>
       </c>
       <c r="C213" s="2">
         <v>0.41666666666666669</v>
@@ -5071,7 +5071,7 @@
         <v>32051</v>
       </c>
       <c r="B216" s="1">
-        <v>32082</v>
+        <v>32083</v>
       </c>
       <c r="C216" s="2">
         <v>0.41666666666666669</v>
@@ -5113,7 +5113,7 @@
         <v>32112</v>
       </c>
       <c r="B218" s="1">
-        <v>32143</v>
+        <v>32146</v>
       </c>
       <c r="C218" s="2">
         <v>0.41666666666666669</v>
@@ -5197,7 +5197,7 @@
         <v>32234</v>
       </c>
       <c r="B222" s="1">
-        <v>32264</v>
+        <v>32265</v>
       </c>
       <c r="C222" s="2">
         <v>0.41666666666666669</v>
@@ -5302,7 +5302,7 @@
         <v>32387</v>
       </c>
       <c r="B227" s="1">
-        <v>32417</v>
+        <v>32419</v>
       </c>
       <c r="C227" s="2">
         <v>0.41666666666666669</v>
@@ -5365,7 +5365,7 @@
         <v>32478</v>
       </c>
       <c r="B230" s="1">
-        <v>32509</v>
+        <v>32511</v>
       </c>
       <c r="C230" s="2">
         <v>0.41666666666666669</v>
@@ -5428,14 +5428,14 @@
         <v>32568</v>
       </c>
       <c r="B233" s="1">
-        <v>32599</v>
+        <v>32601</v>
       </c>
       <c r="C233" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D233" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E233" s="4">
         <v>51.5</v>
@@ -5491,7 +5491,7 @@
         <v>32660</v>
       </c>
       <c r="B236" s="1">
-        <v>32690</v>
+        <v>32692</v>
       </c>
       <c r="C236" s="2">
         <v>0.41666666666666669</v>
@@ -5554,7 +5554,7 @@
         <v>32752</v>
       </c>
       <c r="B239" s="1">
-        <v>32782</v>
+        <v>32783</v>
       </c>
       <c r="C239" s="2">
         <v>0.41666666666666669</v>
@@ -5617,7 +5617,7 @@
         <v>32843</v>
       </c>
       <c r="B242" s="1">
-        <v>32874</v>
+        <v>32875</v>
       </c>
       <c r="C242" s="2">
         <v>0.41666666666666669</v>
@@ -5680,14 +5680,14 @@
         <v>32933</v>
       </c>
       <c r="B245" s="1">
-        <v>32964</v>
+        <v>32965</v>
       </c>
       <c r="C245" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D245" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E245" s="4">
         <v>49.9</v>
@@ -5743,7 +5743,7 @@
         <v>33025</v>
       </c>
       <c r="B248" s="1">
-        <v>33055</v>
+        <v>33056</v>
       </c>
       <c r="C248" s="2">
         <v>0.41666666666666669</v>
@@ -5785,7 +5785,7 @@
         <v>33086</v>
       </c>
       <c r="B250" s="1">
-        <v>33117</v>
+        <v>33120</v>
       </c>
       <c r="C250" s="2">
         <v>0.41666666666666669</v>
@@ -5848,7 +5848,7 @@
         <v>33178</v>
       </c>
       <c r="B253" s="1">
-        <v>33208</v>
+        <v>33210</v>
       </c>
       <c r="C253" s="2">
         <v>0.41666666666666669</v>
@@ -5869,7 +5869,7 @@
         <v>33208</v>
       </c>
       <c r="B254" s="1">
-        <v>33239</v>
+        <v>33240</v>
       </c>
       <c r="C254" s="2">
         <v>0.41666666666666669</v>
@@ -5974,7 +5974,7 @@
         <v>33359</v>
       </c>
       <c r="B259" s="1">
-        <v>33390</v>
+        <v>33392</v>
       </c>
       <c r="C259" s="2">
         <v>0.41666666666666669</v>
@@ -6052,7 +6052,7 @@
         <v>33451</v>
       </c>
       <c r="B262" s="1">
-        <v>33482</v>
+        <v>33484</v>
       </c>
       <c r="C262" s="2">
         <v>0.41666666666666669</v>
@@ -6115,7 +6115,7 @@
         <v>33543</v>
       </c>
       <c r="B265" s="1">
-        <v>33573</v>
+        <v>33574</v>
       </c>
       <c r="C265" s="2">
         <v>0.41666666666666669</v>
@@ -6136,7 +6136,7 @@
         <v>33573</v>
       </c>
       <c r="B266" s="1">
-        <v>33604</v>
+        <v>33605</v>
       </c>
       <c r="C266" s="2">
         <v>0.41666666666666669</v>
@@ -6157,7 +6157,7 @@
         <v>33604</v>
       </c>
       <c r="B267" s="1">
-        <v>33635</v>
+        <v>33637</v>
       </c>
       <c r="C267" s="2">
         <v>0.41666666666666669</v>
@@ -6178,7 +6178,7 @@
         <v>33635</v>
       </c>
       <c r="B268" s="1">
-        <v>33664</v>
+        <v>33665</v>
       </c>
       <c r="C268" s="2">
         <v>0.41666666666666669</v>
@@ -6283,7 +6283,7 @@
         <v>33786</v>
       </c>
       <c r="B273" s="1">
-        <v>33817</v>
+        <v>33819</v>
       </c>
       <c r="C273" s="2">
         <v>0.41666666666666669</v>
@@ -6346,7 +6346,7 @@
         <v>33878</v>
       </c>
       <c r="B276" s="1">
-        <v>33909</v>
+        <v>33910</v>
       </c>
       <c r="C276" s="2">
         <v>0.41666666666666669</v>
@@ -6388,7 +6388,7 @@
         <v>33939</v>
       </c>
       <c r="B278" s="1">
-        <v>33970</v>
+        <v>33973</v>
       </c>
       <c r="C278" s="2">
         <v>0.41666666666666669</v>
@@ -6472,7 +6472,7 @@
         <v>34060</v>
       </c>
       <c r="B282" s="1">
-        <v>34090</v>
+        <v>34092</v>
       </c>
       <c r="C282" s="2">
         <v>0.41666666666666669</v>
@@ -6535,7 +6535,7 @@
         <v>34151</v>
       </c>
       <c r="B285" s="1">
-        <v>34182</v>
+        <v>34183</v>
       </c>
       <c r="C285" s="2">
         <v>0.41666666666666669</v>
@@ -6640,7 +6640,7 @@
         <v>34304</v>
       </c>
       <c r="B290" s="1">
-        <v>34335</v>
+        <v>34337</v>
       </c>
       <c r="C290" s="2">
         <v>0.41666666666666669</v>
@@ -6724,7 +6724,7 @@
         <v>34425</v>
       </c>
       <c r="B294" s="1">
-        <v>34455</v>
+        <v>34456</v>
       </c>
       <c r="C294" s="2">
         <v>0.41666666666666669</v>
@@ -6829,7 +6829,7 @@
         <v>34578</v>
       </c>
       <c r="B299" s="1">
-        <v>34608</v>
+        <v>34610</v>
       </c>
       <c r="C299" s="2">
         <v>0.41666666666666669</v>
@@ -6892,7 +6892,7 @@
         <v>34669</v>
       </c>
       <c r="B302" s="1">
-        <v>34700</v>
+        <v>34702</v>
       </c>
       <c r="C302" s="2">
         <v>0.41666666666666669</v>
@@ -6955,14 +6955,14 @@
         <v>34759</v>
       </c>
       <c r="B305" s="1">
-        <v>34790</v>
+        <v>34792</v>
       </c>
       <c r="C305" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D305" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E305" s="4">
         <v>52.1</v>
@@ -7018,7 +7018,7 @@
         <v>34851</v>
       </c>
       <c r="B308" s="1">
-        <v>34881</v>
+        <v>34883</v>
       </c>
       <c r="C308" s="2">
         <v>0.41666666666666669</v>
@@ -7081,7 +7081,7 @@
         <v>34943</v>
       </c>
       <c r="B311" s="1">
-        <v>34973</v>
+        <v>34974</v>
       </c>
       <c r="C311" s="2">
         <v>0.41666666666666669</v>
@@ -7144,7 +7144,7 @@
         <v>35034</v>
       </c>
       <c r="B314" s="1">
-        <v>35065</v>
+        <v>35066</v>
       </c>
       <c r="C314" s="2">
         <v>0.41666666666666669</v>
@@ -7249,7 +7249,7 @@
         <v>35186</v>
       </c>
       <c r="B319" s="1">
-        <v>35217</v>
+        <v>35219</v>
       </c>
       <c r="C319" s="2">
         <v>0.41666666666666669</v>
@@ -7312,7 +7312,7 @@
         <v>35278</v>
       </c>
       <c r="B322" s="1">
-        <v>35309</v>
+        <v>35311</v>
       </c>
       <c r="C322" s="2">
         <v>0.41666666666666669</v>
@@ -7390,7 +7390,7 @@
         <v>35370</v>
       </c>
       <c r="B325" s="1">
-        <v>35400</v>
+        <v>35401</v>
       </c>
       <c r="C325" s="2">
         <v>0.41666666666666669</v>
@@ -7411,7 +7411,7 @@
         <v>35400</v>
       </c>
       <c r="B326" s="1">
-        <v>35431</v>
+        <v>35432</v>
       </c>
       <c r="C326" s="2">
         <v>0.41666666666666669</v>
@@ -7432,7 +7432,7 @@
         <v>35431</v>
       </c>
       <c r="B327" s="1">
-        <v>35462</v>
+        <v>35464</v>
       </c>
       <c r="C327" s="2">
         <v>0.41666666666666669</v>
@@ -7453,7 +7453,7 @@
         <v>35462</v>
       </c>
       <c r="B328" s="1">
-        <v>35490</v>
+        <v>35492</v>
       </c>
       <c r="C328" s="2">
         <v>0.41666666666666669</v>
@@ -7516,7 +7516,7 @@
         <v>35551</v>
       </c>
       <c r="B331" s="1">
-        <v>35582</v>
+        <v>35583</v>
       </c>
       <c r="C331" s="2">
         <v>0.41666666666666669</v>
@@ -7579,7 +7579,7 @@
         <v>35643</v>
       </c>
       <c r="B334" s="1">
-        <v>35674</v>
+        <v>35675</v>
       </c>
       <c r="C334" s="2">
         <v>0.41666666666666669</v>
@@ -7621,7 +7621,7 @@
         <v>35704</v>
       </c>
       <c r="B336" s="1">
-        <v>35735</v>
+        <v>35737</v>
       </c>
       <c r="C336" s="2">
         <v>0.41666666666666669</v>
@@ -7663,7 +7663,7 @@
         <v>35765</v>
       </c>
       <c r="B338" s="1">
-        <v>35796</v>
+        <v>35797</v>
       </c>
       <c r="C338" s="2">
         <v>0.41666666666666669</v>
@@ -7684,7 +7684,7 @@
         <v>35796</v>
       </c>
       <c r="B339" s="1">
-        <v>35827</v>
+        <v>35828</v>
       </c>
       <c r="C339" s="2">
         <v>0.41666666666666669</v>
@@ -7705,7 +7705,7 @@
         <v>35827</v>
       </c>
       <c r="B340" s="1">
-        <v>35855</v>
+        <v>35856</v>
       </c>
       <c r="C340" s="2">
         <v>0.41666666666666669</v>
@@ -7810,7 +7810,7 @@
         <v>35977</v>
       </c>
       <c r="B345" s="1">
-        <v>36008</v>
+        <v>36010</v>
       </c>
       <c r="C345" s="2">
         <v>0.41666666666666669</v>
@@ -7873,7 +7873,7 @@
         <v>36069</v>
       </c>
       <c r="B348" s="1">
-        <v>36100</v>
+        <v>36101</v>
       </c>
       <c r="C348" s="2">
         <v>0.41666666666666669</v>
@@ -7915,7 +7915,7 @@
         <v>36130</v>
       </c>
       <c r="B350" s="1">
-        <v>36161</v>
+        <v>36164</v>
       </c>
       <c r="C350" s="2">
         <v>0.41666666666666669</v>
@@ -7999,7 +7999,7 @@
         <v>36251</v>
       </c>
       <c r="B354" s="1">
-        <v>36281</v>
+        <v>36283</v>
       </c>
       <c r="C354" s="2">
         <v>0.41666666666666669</v>
@@ -8062,7 +8062,7 @@
         <v>36342</v>
       </c>
       <c r="B357" s="1">
-        <v>36373</v>
+        <v>36374</v>
       </c>
       <c r="C357" s="2">
         <v>0.41666666666666669</v>
@@ -8167,7 +8167,7 @@
         <v>36495</v>
       </c>
       <c r="B362" s="1">
-        <v>36526</v>
+        <v>36528</v>
       </c>
       <c r="C362" s="2">
         <v>0.41666666666666669</v>
@@ -8230,14 +8230,14 @@
         <v>36586</v>
       </c>
       <c r="B365" s="1">
-        <v>36617</v>
+        <v>36619</v>
       </c>
       <c r="C365" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D365" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E365" s="4">
         <v>54.9</v>
@@ -8293,7 +8293,7 @@
         <v>36678</v>
       </c>
       <c r="B368" s="1">
-        <v>36708</v>
+        <v>36710</v>
       </c>
       <c r="C368" s="2">
         <v>0.41666666666666669</v>
@@ -8356,7 +8356,7 @@
         <v>36770</v>
       </c>
       <c r="B371" s="1">
-        <v>36800</v>
+        <v>36801</v>
       </c>
       <c r="C371" s="2">
         <v>0.41666666666666669</v>
@@ -8419,7 +8419,7 @@
         <v>36861</v>
       </c>
       <c r="B374" s="1">
-        <v>36892</v>
+        <v>36893</v>
       </c>
       <c r="C374" s="2">
         <v>0.41666666666666669</v>
@@ -8482,14 +8482,14 @@
         <v>36951</v>
       </c>
       <c r="B377" s="1">
-        <v>36982</v>
+        <v>36983</v>
       </c>
       <c r="C377" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D377" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E377" s="4">
         <v>43.1</v>
@@ -8545,7 +8545,7 @@
         <v>37043</v>
       </c>
       <c r="B380" s="1">
-        <v>37073</v>
+        <v>37074</v>
       </c>
       <c r="C380" s="2">
         <v>0.41666666666666669</v>
@@ -8587,7 +8587,7 @@
         <v>37104</v>
       </c>
       <c r="B382" s="1">
-        <v>37135</v>
+        <v>37138</v>
       </c>
       <c r="C382" s="2">
         <v>0.41666666666666669</v>
@@ -8650,7 +8650,7 @@
         <v>37196</v>
       </c>
       <c r="B385" s="1">
-        <v>37226</v>
+        <v>37228</v>
       </c>
       <c r="C385" s="2">
         <v>0.41666666666666669</v>
@@ -8671,7 +8671,7 @@
         <v>37226</v>
       </c>
       <c r="B386" s="1">
-        <v>37257</v>
+        <v>37258</v>
       </c>
       <c r="C386" s="2">
         <v>0.41666666666666669</v>
@@ -8791,7 +8791,7 @@
         <v>37377</v>
       </c>
       <c r="B391" s="1">
-        <v>37408</v>
+        <v>37410</v>
       </c>
       <c r="C391" s="2">
         <v>0.41666666666666669</v>
@@ -8854,7 +8854,7 @@
         <v>37469</v>
       </c>
       <c r="B394" s="1">
-        <v>37500</v>
+        <v>37502</v>
       </c>
       <c r="C394" s="2">
         <v>0.41666666666666669</v>
@@ -8917,7 +8917,7 @@
         <v>37561</v>
       </c>
       <c r="B397" s="1">
-        <v>37591</v>
+        <v>37592</v>
       </c>
       <c r="C397" s="2">
         <v>0.41666666666666669</v>
@@ -8938,7 +8938,7 @@
         <v>37591</v>
       </c>
       <c r="B398" s="1">
-        <v>37622</v>
+        <v>37623</v>
       </c>
       <c r="C398" s="2">
         <v>0.41666666666666669</v>
@@ -8959,7 +8959,7 @@
         <v>37622</v>
       </c>
       <c r="B399" s="1">
-        <v>37653</v>
+        <v>37655</v>
       </c>
       <c r="C399" s="2">
         <v>0.41666666666666669</v>
@@ -8980,7 +8980,7 @@
         <v>37653</v>
       </c>
       <c r="B400" s="1">
-        <v>37681</v>
+        <v>37683</v>
       </c>
       <c r="C400" s="2">
         <v>0.41666666666666669</v>
@@ -9043,7 +9043,7 @@
         <v>37742</v>
       </c>
       <c r="B403" s="1">
-        <v>37773</v>
+        <v>37774</v>
       </c>
       <c r="C403" s="2">
         <v>0.41666666666666669</v>
@@ -9106,7 +9106,7 @@
         <v>37834</v>
       </c>
       <c r="B406" s="1">
-        <v>37865</v>
+        <v>37866</v>
       </c>
       <c r="C406" s="2">
         <v>0.41666666666666669</v>
@@ -9148,7 +9148,7 @@
         <v>37895</v>
       </c>
       <c r="B408" s="1">
-        <v>37926</v>
+        <v>37928</v>
       </c>
       <c r="C408" s="2">
         <v>0.41666666666666669</v>
@@ -9190,7 +9190,7 @@
         <v>37956</v>
       </c>
       <c r="B410" s="1">
-        <v>37987</v>
+        <v>37988</v>
       </c>
       <c r="C410" s="2">
         <v>0.41666666666666669</v>
@@ -9211,7 +9211,7 @@
         <v>37987</v>
       </c>
       <c r="B411" s="1">
-        <v>38018</v>
+        <v>38019</v>
       </c>
       <c r="C411" s="2">
         <v>0.41666666666666669</v>
@@ -9274,7 +9274,7 @@
         <v>38078</v>
       </c>
       <c r="B414" s="1">
-        <v>38108</v>
+        <v>38110</v>
       </c>
       <c r="C414" s="2">
         <v>0.41666666666666669</v>
@@ -9337,7 +9337,7 @@
         <v>38169</v>
       </c>
       <c r="B417" s="1">
-        <v>38200</v>
+        <v>38201</v>
       </c>
       <c r="C417" s="2">
         <v>0.41666666666666669</v>
@@ -9442,7 +9442,7 @@
         <v>38322</v>
       </c>
       <c r="B422" s="1">
-        <v>38353</v>
+        <v>38355</v>
       </c>
       <c r="C422" s="2">
         <v>0.41666666666666669</v>
@@ -9526,7 +9526,7 @@
         <v>38443</v>
       </c>
       <c r="B426" s="1">
-        <v>38473</v>
+        <v>38474</v>
       </c>
       <c r="C426" s="2">
         <v>0.41666666666666669</v>
@@ -9631,7 +9631,7 @@
         <v>38596</v>
       </c>
       <c r="B431" s="1">
-        <v>38626</v>
+        <v>38628</v>
       </c>
       <c r="C431" s="2">
         <v>0.41666666666666669</v>
@@ -9694,7 +9694,7 @@
         <v>38687</v>
       </c>
       <c r="B434" s="1">
-        <v>38718</v>
+        <v>38720</v>
       </c>
       <c r="C434" s="2">
         <v>0.41666666666666669</v>
@@ -9757,14 +9757,14 @@
         <v>38777</v>
       </c>
       <c r="B437" s="1">
-        <v>38808</v>
+        <v>38810</v>
       </c>
       <c r="C437" s="2">
         <v>0.41666666666666669</v>
       </c>
       <c r="D437" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>UTC-5</v>
+        <v>UTC-4</v>
       </c>
       <c r="E437" s="4">
         <v>54.3</v>
@@ -9820,7 +9820,7 @@
         <v>38869</v>
       </c>
       <c r="B440" s="1">
-        <v>38899</v>
+        <v>38901</v>
       </c>
       <c r="C440" s="2">
         <v>0.41666666666666669</v>
@@ -9883,7 +9883,7 @@
         <v>38961</v>
       </c>
       <c r="B443" s="1">
-        <v>38991</v>
+        <v>38992</v>
       </c>
       <c r="C443" s="2">
         <v>0.41666666666666669</v>
@@ -9946,7 +9946,7 @@
         <v>39052</v>
       </c>
       <c r="B446" s="1">
-        <v>39083</v>
+        <v>39084</v>
       </c>
       <c r="C446" s="2">
         <v>0.41666666666666669</v>
@@ -10009,7 +10009,7 @@
         <v>39142</v>
       </c>
       <c r="B449" s="1">
-        <v>39173</v>
+        <v>39174</v>
       </c>
       <c r="C449" s="2">
         <v>0.41666666666666669</v>
@@ -10087,7 +10087,7 @@
         <v>39234</v>
       </c>
       <c r="B452" s="1">
-        <v>39264</v>
+        <v>39265</v>
       </c>
       <c r="C452" s="2">
         <v>0.41666666666666669</v>
@@ -10129,7 +10129,7 @@
         <v>39295</v>
       </c>
       <c r="B454" s="1">
-        <v>39326</v>
+        <v>39329</v>
       </c>
       <c r="C454" s="2">
         <v>0.41666666666666669</v>
@@ -10192,7 +10192,7 @@
         <v>39387</v>
       </c>
       <c r="B457" s="1">
-        <v>39417</v>
+        <v>39419</v>
       </c>
       <c r="C457" s="2">
         <v>0.41666666666666669</v>
@@ -10213,7 +10213,7 @@
         <v>39417</v>
       </c>
       <c r="B458" s="1">
-        <v>39448</v>
+        <v>39449</v>
       </c>
       <c r="C458" s="2">
         <v>0.41666666666666669</v>
@@ -14683,7 +14683,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D643" s="3" t="str">
-        <f t="shared" ref="D643:D671" si="10">IF(
+        <f t="shared" ref="D643:D674" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -15383,6 +15383,75 @@
         <v>48.7</v>
       </c>
     </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A672" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B672" s="1">
+        <v>45964</v>
+      </c>
+      <c r="C672" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D672" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="E672" s="4">
+        <v>48.7</v>
+      </c>
+      <c r="F672" s="4">
+        <v>49.4</v>
+      </c>
+      <c r="G672" s="4">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A673" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B673" s="1">
+        <v>45992</v>
+      </c>
+      <c r="C673" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D673" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="E673" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="F673" s="4">
+        <v>49</v>
+      </c>
+      <c r="G673" s="4">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A674" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B674" s="1">
+        <v>45662</v>
+      </c>
+      <c r="C674" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D674" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="F674" s="4">
+        <v>48.3</v>
+      </c>
+      <c r="G674" s="4">
+        <v>48.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/macro/USA/USPMI.xlsx
+++ b/data/macro/USA/USPMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B42470-0C53-40A7-BA5C-FD8421877220}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A0DD0-7A19-49DE-A4A3-1F53127D5173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16605" yWindow="780" windowWidth="19395" windowHeight="20700" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -155,8 +155,8 @@
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -15486,6 +15486,9 @@
         <f t="shared" si="10"/>
         <v>UTC-5</v>
       </c>
+      <c r="E674" s="7">
+        <v>47.9</v>
+      </c>
       <c r="F674" s="7">
         <v>48.3</v>
       </c>

--- a/data/macro/USA/USPMI.xlsx
+++ b/data/macro/USA/USPMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7EC923-4F43-4B28-ADAC-5B16874B75EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3DC889-C406-4301-A049-A5E51A9C47B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16605" yWindow="780" windowWidth="19395" windowHeight="20700" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
   </bookViews>
   <sheets>
     <sheet name="NAPMPMI" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>Release Date</t>
   </si>
@@ -90,9 +99,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.investing.com/economic-calendar/ism-non-manufacturing-pmi-176</t>
-  </si>
-  <si>
     <t>NAPMNNO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -132,6 +138,14 @@
     <t>US ISM PMI New Orders</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-non-manufacturing-pmi-176</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-manufacturing-new-orders-index-1483</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -147,7 +161,7 @@
     <numFmt numFmtId="182" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="183" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -197,6 +211,13 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +244,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -273,6 +294,8 @@
     <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="쉼표" xfId="2" builtinId="3"/>
@@ -4608,6 +4631,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4615,7 +4639,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8962,6 +8985,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8969,7 +8993,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10142,6 +10165,9 @@
                 <c:pt idx="343">
                   <c:v>46085</c:v>
                 </c:pt>
+                <c:pt idx="344">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11179,6 +11205,9 @@
                 </c:pt>
                 <c:pt idx="342">
                   <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>56.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11325,6 +11354,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11332,7 +11362,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13466,15 +13495,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF67A92-ADBD-0745-9FE5-B9C5971015D9}">
-  <dimension ref="A1:G676"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G678"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="7" customWidth="1"/>
-    <col min="5" max="7" width="10.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="5"/>
+    <col min="5" max="7" width="10.90625" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.54296875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -27683,7 +27712,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D676" si="10">IF(
+        <f t="shared" ref="D643:D678" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -28503,6 +28532,48 @@
         <v>52.6</v>
       </c>
     </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B677" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C677" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D677" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E677" s="14">
+        <v>52.7</v>
+      </c>
+      <c r="F677" s="14">
+        <v>52.3</v>
+      </c>
+      <c r="G677" s="14">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A678" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B678" s="6">
+        <v>46143</v>
+      </c>
+      <c r="C678" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D678" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G678" s="14">
+        <v>52.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28512,15 +28583,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211418AD-A92B-4993-8F85-2AEBF0BA6CBF}">
-  <dimension ref="A1:G676"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G678"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="7" customWidth="1"/>
-    <col min="5" max="7" width="8.88671875" style="14"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="5" max="7" width="8.90625" style="14"/>
+    <col min="8" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -42192,7 +42263,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D676" si="10">IF(
+        <f t="shared" ref="D643:D678" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -42961,6 +43032,48 @@
         <v>57.1</v>
       </c>
     </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B677" s="19">
+        <v>46113</v>
+      </c>
+      <c r="C677" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D677" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E677" s="14">
+        <v>53.5</v>
+      </c>
+      <c r="F677" s="14">
+        <v>54.5</v>
+      </c>
+      <c r="G677" s="14">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A678" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B678" s="19">
+        <v>46143</v>
+      </c>
+      <c r="C678" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D678" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G678" s="14">
+        <v>53.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42969,15 +43082,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFF2CEE-C6DC-443A-8BCC-B45C1FB035BB}">
-  <dimension ref="A1:G345"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G346"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" style="7" customWidth="1"/>
-    <col min="5" max="7" width="8.88671875" style="16"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="11.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" style="7" customWidth="1"/>
+    <col min="5" max="7" width="8.90625" style="16"/>
+    <col min="8" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -50424,7 +50537,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="7" t="str">
-        <f t="shared" ref="D323:D345" si="5">IF(
+        <f t="shared" ref="D323:D346" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -50958,7 +51071,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="6">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="B345" s="6">
         <v>46085</v>
@@ -50970,8 +51083,38 @@
         <f t="shared" si="5"/>
         <v>UTC-5</v>
       </c>
+      <c r="E345" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="F345" s="16">
+        <v>53.5</v>
+      </c>
       <c r="G345" s="16">
         <v>53.8</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A346" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B346" s="6">
+        <v>46118</v>
+      </c>
+      <c r="C346" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D346" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E346" s="16">
+        <v>54</v>
+      </c>
+      <c r="F346" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="G346" s="16">
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -50982,15 +51125,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A96048-4AA7-4D08-9D09-84880E5018F3}">
-  <dimension ref="A1:G345"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G346"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="8" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -57888,7 +58031,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="8" t="str">
-        <f t="shared" ref="D323:D345" si="5">IF(
+        <f t="shared" ref="D323:D346" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -58419,12 +58562,42 @@
         <f t="shared" si="5"/>
         <v>UTC-5</v>
       </c>
+      <c r="E345" s="9">
+        <v>58.6</v>
+      </c>
+      <c r="F345" s="9">
+        <v>53.5</v>
+      </c>
       <c r="G345" s="9">
         <v>53.1</v>
       </c>
     </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A346" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B346" s="6">
+        <v>46118</v>
+      </c>
+      <c r="C346" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D346" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E346" s="9">
+        <v>60.6</v>
+      </c>
+      <c r="F346" s="9">
+        <v>56.8</v>
+      </c>
+      <c r="G346" s="9">
+        <v>58.6</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G343">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G343">
     <sortCondition ref="B2:B343"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -58435,15 +58608,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E166FA-B3BC-434C-8634-D7F9CA2C884E}">
-  <dimension ref="A1:G345"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G346"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="8" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -65344,7 +65517,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="8" t="str">
-        <f t="shared" ref="D323:D345" si="5">IF(
+        <f t="shared" ref="D323:D346" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -65878,12 +66051,39 @@
         <f t="shared" si="5"/>
         <v>UTC-5</v>
       </c>
+      <c r="E345" s="9">
+        <v>51.8</v>
+      </c>
       <c r="G345" s="9">
         <v>50.3</v>
       </c>
     </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A346" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B346" s="6">
+        <v>46118</v>
+      </c>
+      <c r="C346" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D346" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E346" s="9">
+        <v>45.2</v>
+      </c>
+      <c r="F346" s="9">
+        <v>51</v>
+      </c>
+      <c r="G346" s="9">
+        <v>51.8</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G343">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G343">
     <sortCondition ref="B2:B343"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -65894,7 +66094,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F3DB92-597C-48B7-9A53-C7EC52B4B614}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -65906,14 +66106,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADD8639-870D-4A57-ACB7-1E30693D2504}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="5"/>
-    <col min="2" max="2" width="26.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="72.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="8.90625" style="5"/>
+    <col min="2" max="2" width="26.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="72.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -65927,7 +66127,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -65941,22 +66141,27 @@
         <v>13</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -65966,28 +66171,28 @@
       <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
+      <c r="D5" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -65995,24 +66200,27 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{E30A90E7-EC36-4BF2-964C-CA813D2223A4}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{DD927D0E-247D-4425-883B-E647A414E90A}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{217F9969-5E1C-485D-B533-BC37BAE3F0EF}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{F972C882-35AB-492A-9F06-5249EC581123}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/data/macro/USA/USPMI.xlsx
+++ b/data/macro/USA/USPMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3DC889-C406-4301-A049-A5E51A9C47B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D402A0E6-9F9F-49CF-851A-50C293CDA31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
   </bookViews>
   <sheets>
     <sheet name="NAPMPMI" sheetId="1" r:id="rId1"/>
@@ -10167,6 +10167,9 @@
                 </c:pt>
                 <c:pt idx="344">
                   <c:v>46118</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>46147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -28570,6 +28573,12 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E678" s="14">
+        <v>52.7</v>
+      </c>
+      <c r="F678" s="14">
+        <v>53.1</v>
+      </c>
       <c r="G678" s="14">
         <v>52.7</v>
       </c>
@@ -43070,6 +43079,12 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E678" s="14">
+        <v>54.1</v>
+      </c>
+      <c r="F678" s="14">
+        <v>54.5</v>
+      </c>
       <c r="G678" s="14">
         <v>53.5</v>
       </c>
@@ -43082,7 +43097,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFF2CEE-C6DC-443A-8BCC-B45C1FB035BB}">
-  <dimension ref="A1:G346"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1796875" style="6" bestFit="1" customWidth="1"/>
@@ -50537,7 +50552,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="7" t="str">
-        <f t="shared" ref="D323:D346" si="5">IF(
+        <f t="shared" ref="D323:D347" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -51117,6 +51132,30 @@
         <v>56.1</v>
       </c>
     </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A347" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B347" s="6">
+        <v>46147</v>
+      </c>
+      <c r="C347" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D347" s="7" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E347" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="F347" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G347" s="16">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51125,10 +51164,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A96048-4AA7-4D08-9D09-84880E5018F3}">
-  <dimension ref="A1:G346"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.90625" style="10" bestFit="1" customWidth="1"/>
@@ -58031,7 +58070,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="8" t="str">
-        <f t="shared" ref="D323:D346" si="5">IF(
+        <f t="shared" ref="D323:D347" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -58596,6 +58635,30 @@
         <v>58.6</v>
       </c>
     </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A347" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B347" s="6">
+        <v>46147</v>
+      </c>
+      <c r="C347" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D347" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E347" s="9">
+        <v>53.5</v>
+      </c>
+      <c r="F347" s="9">
+        <v>57.3</v>
+      </c>
+      <c r="G347" s="9">
+        <v>60.6</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G343">
     <sortCondition ref="B2:B343"/>
@@ -58608,7 +58671,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E166FA-B3BC-434C-8634-D7F9CA2C884E}">
-  <dimension ref="A1:G346"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
@@ -65517,7 +65580,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D323" s="8" t="str">
-        <f t="shared" ref="D323:D346" si="5">IF(
+        <f t="shared" ref="D323:D347" si="5">IF(
  AND(
   B323 &gt;= IF(
          YEAR(B323)&gt;=2007,
@@ -66080,6 +66143,30 @@
       </c>
       <c r="G346" s="9">
         <v>51.8</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A347" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B347" s="6">
+        <v>46147</v>
+      </c>
+      <c r="C347" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D347" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E347" s="9">
+        <v>48</v>
+      </c>
+      <c r="F347" s="9">
+        <v>48.3</v>
+      </c>
+      <c r="G347" s="9">
+        <v>45.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/USPMI.xlsx
+++ b/data/macro/USA/USPMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D402A0E6-9F9F-49CF-851A-50C293CDA31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8676ADF6-126A-4751-939C-2328CCD9D11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DE2917F-A9F0-C04F-BB97-3733FD6C8746}"/>
   </bookViews>
   <sheets>
     <sheet name="NAPMPMI" sheetId="1" r:id="rId1"/>
@@ -152,33 +152,33 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="183" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="169" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -200,7 +200,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -238,60 +238,60 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
@@ -13499,14 +13499,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF67A92-ADBD-0745-9FE5-B9C5971015D9}">
   <dimension ref="A1:G678"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.8984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="7" customWidth="1"/>
-    <col min="5" max="7" width="10.90625" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.54296875" style="5"/>
+    <col min="5" max="7" width="10.8984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.5" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -28593,14 +28593,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211418AD-A92B-4993-8F85-2AEBF0BA6CBF}">
   <dimension ref="A1:G678"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="7" customWidth="1"/>
-    <col min="5" max="7" width="8.90625" style="14"/>
-    <col min="8" max="16384" width="8.90625" style="5"/>
+    <col min="5" max="7" width="8.8984375" style="14"/>
+    <col min="8" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -43098,14 +43098,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFF2CEE-C6DC-443A-8BCC-B45C1FB035BB}">
   <dimension ref="A1:G347"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" style="7" customWidth="1"/>
-    <col min="5" max="7" width="8.90625" style="16"/>
-    <col min="8" max="16384" width="8.90625" style="5"/>
+    <col min="1" max="1" width="11.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" style="7" customWidth="1"/>
+    <col min="5" max="7" width="8.8984375" style="16"/>
+    <col min="8" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -51165,14 +51165,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A96048-4AA7-4D08-9D09-84880E5018F3}">
   <dimension ref="A1:G347"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.8984375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.90625" style="5"/>
+    <col min="8" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -58672,14 +58672,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E166FA-B3BC-434C-8634-D7F9CA2C884E}">
   <dimension ref="A1:G347"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.8984375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.90625" style="5"/>
+    <col min="8" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -66181,7 +66181,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F3DB92-597C-48B7-9A53-C7EC52B4B614}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -66193,14 +66193,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADD8639-870D-4A57-ACB7-1E30693D2504}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="5"/>
-    <col min="2" max="2" width="26.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="72.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="5"/>
+    <col min="1" max="1" width="8.8984375" style="5"/>
+    <col min="2" max="2" width="26.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="72.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -66234,7 +66234,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
